--- a/artfynd/A 40179-2025 artfynd.xlsx
+++ b/artfynd/A 40179-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>89118911</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534260.8150181465</v>
+        <v>534261</v>
       </c>
       <c r="R2" t="n">
-        <v>6907764.119817353</v>
+        <v>6907764</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2020-07-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>89118912</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534329.0120182114</v>
+        <v>534329</v>
       </c>
       <c r="R3" t="n">
-        <v>6907747.137750532</v>
+        <v>6907747</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2020-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +866,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89118914</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sjudarberget med omgivningar, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>534381</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6907887</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
